--- a/validacao/rotulos_gabriel.xlsx
+++ b/validacao/rotulos_gabriel.xlsx
@@ -442,9 +442,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -466,9 +464,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-    </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -518,9 +514,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
@@ -616,6 +610,21 @@
           <t>https://github.com/openclaw/openclaw</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Assistente pessoal com apps nativos e gateway; releases trazem dmg, zip e pacote npm.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -631,6 +640,21 @@
           <t>https://github.com/tauri-apps/tauri</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Monorepo do framework; cada release corresponde a um pacote publicado no crates.io ou npm.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -646,6 +670,21 @@
           <t>https://github.com/keras-team/keras</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Framework Python usado como dependência em outros projetos; versões publicadas no PyPI.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -661,6 +700,21 @@
           <t>https://github.com/ClickHouse/ClickHouse</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Banco de dados analítico implantado como servidor; releases trazem binários, deb, rpm e tgz.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -676,6 +730,21 @@
           <t>https://github.com/react/react-native</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Framework para apps nativos; cada versão sai no npm e Maven.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -691,6 +760,21 @@
           <t>https://github.com/pyenv/pyenv</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gerenciador de versões do Python via linha de comando; cada tag é empacotada no Homebrew.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -706,6 +790,21 @@
           <t>https://github.com/nuxt/nuxt</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Framework web sobre Vue usado como dependência; versões publicadas no npm.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -721,6 +820,21 @@
           <t>https://github.com/facebookresearch/faiss</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Biblioteca de busca vetorial; releases viram pacotes conda e pip.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -736,6 +850,21 @@
           <t>https://github.com/BerriAI/litellm</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gateway implantado como serviço via Docker; também oferece SDK Python e builds dev frequentes.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -751,6 +880,21 @@
           <t>https://github.com/microsoft/vscode</t>
         </is>
       </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Editor usado direto pelo usuário; cada tag corresponde a uma versão distribuída do VS Code.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -766,6 +910,21 @@
           <t>https://github.com/remotion-dev/remotion</t>
         </is>
       </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>framework React para gerar vídeos; cada versão sai no npm junto com os pacotes</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -781,6 +940,21 @@
           <t>https://github.com/alibaba/open-code-review</t>
         </is>
       </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>revisor de código usado pela linha de comando; releases trazem binários por plataforma</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -796,6 +970,21 @@
           <t>https://github.com/pocketbase/pocketbase</t>
         </is>
       </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>backend completo em um executável, implantado como serviço; releases trazem os binários</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -811,6 +1000,21 @@
           <t>https://github.com/TanStack/query</t>
         </is>
       </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>biblioteca de busca e cache de dados; cada release é um pacote publicado no npm</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -826,6 +1030,21 @@
           <t>https://github.com/mrdoob/three.js</t>
         </is>
       </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>biblioteca 3D em JavaScript; cada release mensal vira uma versão do pacote three</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -841,6 +1060,21 @@
           <t>https://github.com/prometheus/prometheus</t>
         </is>
       </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>sistema de monitoramento implantado como serviço; releases trazem binários para várias plataformas</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -856,6 +1090,21 @@
           <t>https://github.com/vllm-project/vllm</t>
         </is>
       </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>motor de inferência implantado como servidor, também usado como biblioteca; releases trazem pacotes Python</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -871,6 +1120,21 @@
           <t>https://github.com/payloadcms/payload</t>
         </is>
       </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>framework Next.js usado como dependência; cada versão é publicada no npm</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -886,6 +1150,21 @@
           <t>https://github.com/jgm/pandoc</t>
         </is>
       </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>conversor de documentos usado na linha de comando; releases trazem instaladores e binários</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -901,6 +1180,21 @@
           <t>https://github.com/mattpocock/skills</t>
         </is>
       </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>outro</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>coleção de skills em markdown, não é biblioteca nem programa; versões atualizam o plugin</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -916,6 +1210,21 @@
           <t>https://github.com/chakra-ui/chakra-ui</t>
         </is>
       </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Biblioteca de componentes React; cada release corresponde a um pacote publicado no npm.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -931,6 +1240,21 @@
           <t>https://github.com/fastlane/fastlane</t>
         </is>
       </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Programa de linha de comando para automação mobile; cada release traz a gem publicada.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -946,6 +1270,21 @@
           <t>https://github.com/shadcn-ui/ui</t>
         </is>
       </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Componentes reutilizados em outros projetos via CLI shadcn; releases são versões publicadas no npm.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -961,6 +1300,21 @@
           <t>https://github.com/sickn33/agentic-awesome-skills</t>
         </is>
       </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>outro</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Catálogo de skills em Markdown para agentes; as versões são instaladas via npx ou clone.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -976,6 +1330,21 @@
           <t>https://github.com/ethereum/go-ethereum</t>
         </is>
       </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Cliente de nó Ethereum; cada release gera binários e imagens para os operadores.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -991,6 +1360,21 @@
           <t>https://github.com/Significant-Gravitas/AutoGPT</t>
         </is>
       </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Plataforma de agentes; publicar uma release dispara o deploy em produção.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1006,6 +1390,21 @@
           <t>https://github.com/upstash/context7</t>
         </is>
       </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Servidor MCP e CLI de documentação para agentes; releases são pacotes publicados no npm.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1021,6 +1420,21 @@
           <t>https://github.com/xtekky/gpt4free</t>
         </is>
       </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Pacote Python que também oferece GUI e API; releases trazem wheel, executáveis e Docker.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1036,6 +1450,21 @@
           <t>https://github.com/langgenius/dify</t>
         </is>
       </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Plataforma implantada em nuvem ou self-hosted; cada release gera imagens Docker e guia de upgrade.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1051,6 +1480,21 @@
           <t>https://github.com/roboflow/supervision</t>
         </is>
       </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Biblioteca Python de visão computacional; cada release é publicada no PyPI.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1066,6 +1510,21 @@
           <t>https://github.com/Fission-AI/OpenSpec</t>
         </is>
       </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>CLI instalada pelo npm; cada release corresponde a uma versão publicada do pacote</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1081,6 +1540,21 @@
           <t>https://github.com/mastodon/mastodon</t>
         </is>
       </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>servidor de rede social auto-hospedado; admins atualizam a instância a cada versão</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1096,6 +1570,21 @@
           <t>https://github.com/Mintplex-Labs/anything-llm</t>
         </is>
       </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>app desktop e docker usado direto pelo usuário; releases trazem instaladores e versões</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1111,6 +1600,21 @@
           <t>https://github.com/Imbad0202/academic-research-skills</t>
         </is>
       </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>outro</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>coleção de skills e scripts instalada como plugin; o manifesto acompanha cada release</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1126,6 +1630,21 @@
           <t>https://github.com/pingcap/tidb</t>
         </is>
       </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>banco de dados distribuído implantado como serviço; cada tag é uma versão oficial</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1141,6 +1660,21 @@
           <t>https://github.com/ggml-org/llama.cpp</t>
         </is>
       </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>biblioteca C/C++; releases b#### são builds automáticos por commit, tratados como nightly</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1156,6 +1690,21 @@
           <t>https://github.com/ChrisTitusTech/winutil</t>
         </is>
       </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>utilitário gráfico para Windows; cada release publica o script que o usuário executa</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1171,6 +1720,21 @@
           <t>https://github.com/crewAIInc/crewAI</t>
         </is>
       </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>framework Python usado como dependência; cada release corresponde a uma versão no PyPI</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1186,6 +1750,21 @@
           <t>https://github.com/ToolJet/ToolJet</t>
         </is>
       </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>plataforma low-code auto-hospedada; versões LTS saem como imagens docker para instalação</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1201,6 +1780,21 @@
           <t>https://github.com/browser-use/browser-use</t>
         </is>
       </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>biblioteca Python de automação de navegador; cada release vira versão publicada no PyPI</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1216,6 +1810,21 @@
           <t>https://github.com/danielmiessler/Fabric</t>
         </is>
       </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>CLI em Go com binarios publicados a cada versao para varios sistemas</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1231,6 +1840,21 @@
           <t>https://github.com/career-ops-hq/career-ops</t>
         </is>
       </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>incerto</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>app local de busca de vagas; ate a v1.34 atualizacoes vinham da main</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1246,6 +1870,21 @@
           <t>https://github.com/vercel-labs/agent-browser</t>
         </is>
       </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>CLI de automacao de navegador, publicada no npm e com binarios por release</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1261,6 +1900,21 @@
           <t>https://github.com/ant-design/ant-design</t>
         </is>
       </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>biblioteca de componentes React publicada no npm a cada versao</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1276,6 +1930,21 @@
           <t>https://github.com/ccxt/ccxt</t>
         </is>
       </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>biblioteca de trading publicada em npm, PyPI e outros registros por versao</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1291,6 +1960,21 @@
           <t>https://github.com/apple/container</t>
         </is>
       </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>CLI para macOS com instalador pkg assinado em cada release</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1306,6 +1990,21 @@
           <t>https://github.com/reactive-resume/reactive-resume</t>
         </is>
       </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>app web auto-hospedavel; releases publicadas como imagens Docker</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1321,6 +2020,21 @@
           <t>https://github.com/rails/rails</t>
         </is>
       </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>framework web; cada release corresponde a gems publicadas</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1336,6 +2050,21 @@
           <t>https://github.com/fastapi/fastapi</t>
         </is>
       </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>framework Python publicado no PyPI a cada versao</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1351,6 +2080,21 @@
           <t>https://github.com/react-hook-form/react-hook-form</t>
         </is>
       </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>biblioteca React de formularios publicada no npm a cada versao</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1366,6 +2110,21 @@
           <t>https://github.com/moeru-ai/airi</t>
         </is>
       </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>App de companheira virtual; cada release traz instaladores para desktop e Android</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1381,6 +2140,21 @@
           <t>https://github.com/janhq/jan</t>
         </is>
       </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>App desktop de chat com modelos locais; releases trazem instaladores para cada sistema</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1396,6 +2170,21 @@
           <t>https://github.com/rtk-ai/rtk</t>
         </is>
       </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Proxy de linha de comando em Rust; releases trazem binários e pacotes deb/rpm</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1411,6 +2200,21 @@
           <t>https://github.com/calcom/cal.diy</t>
         </is>
       </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Plataforma de agendamento auto-hospedada; sem anexos, mas versões viram imagens Docker</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1426,6 +2230,21 @@
           <t>https://github.com/zed-industries/zed</t>
         </is>
       </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Editor de código; toda release traz binários para macOS, Linux e Windows</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1441,6 +2260,21 @@
           <t>https://github.com/typst/typst</t>
         </is>
       </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Compilador com CLI; releases distribuem binários prontos para várias plataformas</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1456,6 +2290,21 @@
           <t>https://github.com/denoland/deno</t>
         </is>
       </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Runtime usado pela linha de comando; releases trazem binários para cada plataforma</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1471,6 +2320,21 @@
           <t>https://github.com/dani-garcia/vaultwarden</t>
         </is>
       </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Servidor auto-hospedado; releases sem anexos, mas cada versão sai como imagem Docker</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1486,6 +2350,21 @@
           <t>https://github.com/nexu-io/open-design</t>
         </is>
       </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>aplicacao/servico</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>App desktop de design colaborativo; releases trazem instaladores para macOS e Windows</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1499,6 +2378,21 @@
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>https://github.com/JuliaLang/julia</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>outro</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Linguagem de programação; cada release é uma versão oficial que o usuário instala</t>
         </is>
       </c>
     </row>
@@ -1674,6 +2568,16 @@
           <t>https://github.com/openclaw/openclaw/compare/v1.2.0...v1.2.1</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Notas citam heartbeat, mas o único código novo corrige detecção de mídia.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1707,6 +2611,16 @@
           <t>https://github.com/openclaw/openclaw/compare/v2026.1.11...v2026.1.11-1</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Hotfix da instalação via npm, que falhava sem a pasta patches.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1740,6 +2654,16 @@
           <t>https://github.com/openclaw/openclaw/compare/v2026.2.21...v2026.2.22</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Release regular com novo provedor, auto-updater e vários recursos, além de correções.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1773,6 +2697,16 @@
           <t>https://github.com/openclaw/openclaw/compare/v2026.2.23...v2026.2.24</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Release regular: onboarding novo no Android e mudanças breaking, junto de muitas correções.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1806,6 +2740,16 @@
           <t>https://github.com/openclaw/openclaw/compare/v2026.5.7...v2026.5.12</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Release grande com instalação mais enxuta e muitos recursos novos.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1839,6 +2783,16 @@
           <t>https://github.com/tauri-apps/tauri/compare/tauri-build-v2.5.0...tauri-v2.9.0</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Versão minor com quatro recursos novos e só duas correções.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1872,6 +2826,16 @@
           <t>https://github.com/tauri-apps/tauri/compare/@tauri-apps/api-v2.11.0...tauri-utils-v2.9.0</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Versão minor com recursos novos, como janelas múltiplas no mobile.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1905,6 +2869,16 @@
           <t>https://github.com/tauri-apps/tauri/compare/tauri-v2.11.2...@tauri-apps/cli-v2.11.2</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Só atualiza o tauri-cli, que traz correções de regressões no empacotamento de recursos.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1938,6 +2912,16 @@
           <t>https://github.com/tauri-apps/tauri/compare/tauri-codegen-v3.0.0-alpha.0...tauri-macros-v3.0.0-alpha.0</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Primeiro alpha da versão 3 com recursos novos.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1971,6 +2955,16 @@
           <t>https://github.com/tauri-apps/tauri/compare/tauri-v3.0.0-alpha.4...tauri-runtime-wry-v3.0.0-alpha.4</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Alpha da versão 3 com atualização de dependências e mudança breaking.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2004,6 +2998,16 @@
           <t>https://github.com/keras-team/keras/compare/v3.11.3...v3.12.0</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Versão minor com API de destilação e quantização GPTQ.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2037,6 +3041,16 @@
           <t>https://github.com/keras-team/keras/compare/v3.12.1...v3.14.0</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Versão minor com checkpoints Orbax, novas quantizações e novo otimizador.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2070,6 +3084,16 @@
           <t>https://github.com/keras-team/keras/compare/v3.14.1...v3.15.0</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Versão minor com exportação para PyTorch e várias operações novas.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2103,6 +3127,16 @@
           <t>https://github.com/keras-team/keras/compare/v3.15.0...v3.12.3</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Patch de segurança contra ataques no carregamento e desserialização de modelos.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2136,6 +3170,16 @@
           <t>https://github.com/keras-team/keras/compare/v3.12.3...v3.15.1</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Patch com correções de segurança e de bugs, sem recursos novos.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2169,6 +3213,16 @@
           <t>https://github.com/ClickHouse/ClickHouse/compare/v25.8.11.66-lts...v25.9.5.21-stable</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Patch estável com backports de correções de bugs e travamentos.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2202,6 +3256,16 @@
           <t>https://github.com/ClickHouse/ClickHouse/compare/v25.10.3.100-stable...v25.8.12.129-lts</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Patch LTS dominado por backports de correções de falhas e travamentos.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2235,6 +3299,16 @@
           <t>https://github.com/ClickHouse/ClickHouse/compare/v26.2.6.27-stable...v26.2.7.17-stable</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Patch estável só com backports de correções, incluindo vazamento de dados entre usuários.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2268,6 +3342,16 @@
           <t>https://github.com/ClickHouse/ClickHouse/compare/v26.3.10.60-lts...v26.1.12.23-stable</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Patch estável com backports, na maioria correções de bugs e de segurança.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2301,6 +3385,16 @@
           <t>https://github.com/ClickHouse/ClickHouse/compare/v26.6.2.160-stable...v26.7.3.19-stable</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Patch estável com correções de travamentos e falhas, além de atualizar dependências.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2334,6 +3428,16 @@
           <t>https://github.com/react/react-native/compare/v0.81.4...v0.82.0</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Nova versão minor do framework, com recursos e mudanças de arquitetura.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2367,6 +3471,16 @@
           <t>https://github.com/react/react-native/compare/v0.83.2...v0.81.6</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Patch da linha 0.81 focado em correções de build, iOS e Android.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2400,6 +3514,16 @@
           <t>https://github.com/react/react-native/compare/v0.81.6...v0.84.0</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Nova versão minor, com recursos e mudanças acumuladas desde a 0.83.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2433,6 +3557,16 @@
           <t>https://github.com/react/react-native/compare/v0.83.9...v0.85.3</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Patch que corrige falhas de build no iOS e na versão do Hermes.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2466,6 +3600,16 @@
           <t>https://github.com/react/react-native/compare/v0.86.2...v0.87.0</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Nova versão minor com recursos e mudanças de API.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2499,6 +3643,16 @@
           <t>https://github.com/pyenv/pyenv/compare/v2.6.21...v2.6.22</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Só adiciona a definição do CPython 3.13.12, atualização de rotina.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2532,6 +3686,16 @@
           <t>https://github.com/pyenv/pyenv/compare/v2.6.23...v2.6.24</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Rotina: novas versões do CPython e Anaconda, ajustes de CI e rehash.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2565,6 +3729,16 @@
           <t>https://github.com/pyenv/pyenv/compare/v2.6.29...v2.6.30</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Rotina: adiciona 3.16-dev e aponta 3.15-dev para a branch de manutenção.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2598,6 +3772,16 @@
           <t>https://github.com/pyenv/pyenv/compare/v2.6.32...v2.7.1</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Traz a opção init --install e novas versões, com poucos ajustes pontuais.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2631,6 +3815,16 @@
           <t>https://github.com/pyenv/pyenv/compare/v2.7.2...v2.7.3</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Rotina: adiciona CPython 3.15.0b3 e melhora scripts de CI.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2664,6 +3858,16 @@
           <t>https://github.com/nuxt/nuxt/compare/v4.2.2...v3.21.0</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Versão minor da linha 3 com recursos portados da 4.3.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2697,6 +3901,16 @@
           <t>https://github.com/nuxt/nuxt/compare/v4.3.1...v4.4.0</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Versão minor com createUseFetch, vue-router 5 e outros recursos.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2730,6 +3944,16 @@
           <t>https://github.com/nuxt/nuxt/compare/v3.21.5...v4.4.5</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Patch com 18 correções e uma melhoria de desempenho, sem recursos novos.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2763,6 +3987,16 @@
           <t>https://github.com/nuxt/nuxt/compare/v3.21.8...v4.4.8</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Hotfix para o servidor de desenvolvimento que falhava no macOS.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2796,6 +4030,16 @@
           <t>https://github.com/nuxt/nuxt/compare/v3.21.10...v4.5.2</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Patch dominado por correções de bugs, com alguns ganhos de desempenho.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2829,6 +4073,16 @@
           <t>https://github.com/facebookresearch/faiss/compare/v1.12.0...v1.13.0</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Versão minor com Panorama, RaBitQ Fast Scan e outros recursos.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2862,6 +4116,16 @@
           <t>https://github.com/facebookresearch/faiss/compare/v1.13.0...v1.13.1</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Patch que traz mais recursos novos do que correções.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2895,6 +4159,16 @@
           <t>https://github.com/facebookresearch/faiss/compare/v1.14.1...v1.14.2</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Release com muitos recursos novos, como SuperKMeans e backend Metal.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2928,6 +4202,16 @@
           <t>https://github.com/facebookresearch/faiss/compare/v1.14.3...v1.15.0</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Versão minor com novos quantizadores, índices e kernels.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2961,6 +4245,16 @@
           <t>https://github.com/facebookresearch/faiss/compare/v1.15.0...v1.15.1</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Mistura correções com 13 recursos novos e otimizações, sem foco corretivo.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2994,6 +4288,16 @@
           <t>https://github.com/BerriAI/litellm/compare/v1.79.dev.1...v1.79.3.dev2</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Build dev que traz principalmente um novo hook de guardrail da Zscaler.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -3027,6 +4331,16 @@
           <t>https://github.com/BerriAI/litellm/compare/v1.80.5.dev32...v1.80.6-nightly</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Nightly com vários recursos novos e poucas correções.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3060,6 +4374,16 @@
           <t>https://github.com/BerriAI/litellm/compare/v1.81.14.dev.1...v1.82.3.dev.3</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Desde a build anterior entrou só uma correção de traces no Langfuse.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3093,6 +4417,16 @@
           <t>https://github.com/BerriAI/litellm/compare/v1.96.2...v1.97.0</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Versão minor com dezenas de recursos novos misturados a correções.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3126,6 +4460,16 @@
           <t>https://github.com/BerriAI/litellm/compare/v1.100.4...v1.101.3</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Patch só com correção de segurança nos tokens de sessão da UI e CLI.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3159,6 +4503,16 @@
           <t>https://github.com/microsoft/vscode/compare/1.104.2...1.104.3</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Release de recuperação que corrige problemas da 1.104 atualizando o proxy-agent.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3192,6 +4546,16 @@
           <t>https://github.com/microsoft/vscode/compare/1.106.1...1.106.2</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Release de recuperação com correções de bugs e regressões da 1.106.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3225,6 +4589,16 @@
           <t>https://github.com/microsoft/vscode/compare/1.126.0...1.127.0</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Release mensal regular com recursos novos de chat e agentes.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3258,6 +4632,16 @@
           <t>https://github.com/microsoft/vscode/compare/1.136.1...1.136.2</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Patch de segurança com várias correções do MSRC, como path traversal.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3291,6 +4675,16 @@
           <t>https://github.com/microsoft/vscode/compare/1.139.0...1.139.1</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Cherry-pick que corrige perda de políticas em falhas temporárias de atualização.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3324,6 +4718,16 @@
           <t>https://github.com/remotion-dev/remotion/compare/v4.0.388...v4.0.390</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>duas correções, mas o grosso é o suporte novo a texto no web renderer</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3357,6 +4761,16 @@
           <t>https://github.com/remotion-dev/remotion/compare/v4.0.390...v4.0.391</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>praticamente só correções de bugs em áudio, player e web renderer</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -3390,6 +4804,16 @@
           <t>https://github.com/remotion-dev/remotion/compare/v4.0.482...v4.0.483</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>vários recursos novos no Studio e efeitos, com algumas correções no meio</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -3423,6 +4847,16 @@
           <t>https://github.com/remotion-dev/remotion/compare/v4.0.501...v4.0.502</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Rspack deixa de ser experimental, render de vários frames e melhorias no Studio</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -3456,6 +4890,16 @@
           <t>https://github.com/remotion-dev/remotion/compare/v4.0.506...v4.0.507</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>muitos recursos novos no Studio, misturados a correções de reprodução de áudio</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3489,6 +4933,16 @@
           <t>https://github.com/alibaba/open-code-review/compare/v1.1.10...v1.1.11</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>adiciona suporte a Windows no build, é funcionalidade nova</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3522,6 +4976,16 @@
           <t>https://github.com/alibaba/open-code-review/compare/v1.3.3...v1.3.4</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>única mudança corrige o CI, que dava erro ao publicar no npm</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3555,6 +5019,16 @@
           <t>https://github.com/alibaba/open-code-review/compare/v1.6.3...v1.6.4</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>só documentação e ajustes de CI, sem correção de defeito</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3588,6 +5062,16 @@
           <t>https://github.com/alibaba/open-code-review/compare/v1.9.5...v1.9.6</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>suporte a várias linguagens novas; as correções são secundárias</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -3621,6 +5105,16 @@
           <t>https://github.com/alibaba/open-code-review/compare/v1.12.4...v1.12.5</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>vários recursos novos no viewer e um plugin novo, além de correções</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -3654,6 +5148,16 @@
           <t>https://github.com/pocketbase/pocketbase/compare/v0.30.3...v0.30.4</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>corrige regressão de CSS no campo json introduzida na v0.30.3</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -3687,6 +5191,16 @@
           <t>https://github.com/pocketbase/pocketbase/compare/v0.34.0...v0.22.37</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>backport de correção no autocomplete e Go atualizado por falhas de segurança</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -3720,6 +5234,16 @@
           <t>https://github.com/pocketbase/pocketbase/compare/v0.36.0...v0.36.1</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>reverte otimização da v0.36.0 que prejudicava o uso de índices</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -3753,6 +5277,16 @@
           <t>https://github.com/pocketbase/pocketbase/compare/v0.36.9...v0.37.0</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>nova interface reescrita do zero, com vários recursos novos</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -3786,6 +5320,16 @@
           <t>https://github.com/pocketbase/pocketbase/compare/v0.39.3...v0.39.4</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>redirectURL opcional e nova ordenação são melhorias; ajustes de interface são menores</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -3819,6 +5363,16 @@
           <t>https://github.com/TanStack/query/compare/@tanstack/react-query-next-experimental@5.100.11...@tanstack/react-query-persist-client@5.100.11</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>só atualiza dependências internas do monorepo</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -3852,6 +5406,16 @@
           <t>https://github.com/TanStack/query/compare/@tanstack/solid-query-persist-client@5.100.13...@tanstack/eslint-plugin-query@5.100.13</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>sem notas nem mudanças próprias, só acompanha a versão dos outros pacotes</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -3885,6 +5449,16 @@
           <t>https://github.com/TanStack/query/compare/@tanstack/react-query-devtools@5.100.14...@tanstack/lit-query@0.2.6</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>só atualiza a dependência do query-core</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -3918,6 +5492,16 @@
           <t>https://github.com/TanStack/query/compare/@tanstack/query-sync-storage-persister@5.101.0...@tanstack/angular-query-experimental@5.101.0</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>apenas acompanha a nova versão do query-core</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -3951,6 +5535,16 @@
           <t>https://github.com/TanStack/query/compare/@tanstack/solid-query@5.103.0...@tanstack/query-devtools@5.103.0</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>corrige dependências não declaradas que falhavam em gerenciadores de pacotes estritos</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -3984,6 +5578,16 @@
           <t>https://github.com/mrdoob/three.js/compare/r180...r181</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>release mensal com centenas de commits, recursos e correções misturados</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -4017,6 +5621,16 @@
           <t>https://github.com/mrdoob/three.js/compare/r181...r182</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>release mensal grande, com otimizações, recursos novos e correções</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -4050,6 +5664,16 @@
           <t>https://github.com/mrdoob/three.js/compare/r182...r183</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>release mensal com recursos novos e remoção de código obsoleto</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -4083,6 +5707,16 @@
           <t>https://github.com/mrdoob/three.js/compare/r184...r185</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>release mensal com centenas de mudanças de todo tipo</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -4116,6 +5750,16 @@
           <t>https://github.com/mrdoob/three.js/compare/r185...r186</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>release mensal grande, mistura recursos novos, limpeza e correções</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -4149,6 +5793,16 @@
           <t>https://github.com/prometheus/prometheus/compare/v3.6.0...v3.7.0</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>versão minor com recursos novos de PromQL e federação</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -4182,6 +5836,16 @@
           <t>https://github.com/prometheus/prometheus/compare/v3.9.1...v3.5.1</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>versão LTS sem mudança de código, só atualiza dependências e o Go</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -4215,6 +5879,16 @@
           <t>https://github.com/prometheus/prometheus/compare/v3.11.0...v3.11.1</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>corrige falha de inicialização do tracing OTLP via HTTP com insecure</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -4248,6 +5922,16 @@
           <t>https://github.com/prometheus/prometheus/compare/v3.11.3...v3.12.0</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>versão minor com recursos, desempenho e correções, incluindo duas de segurança</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -4281,6 +5965,16 @@
           <t>https://github.com/prometheus/prometheus/compare/v3.13.3...v3.15.0</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>versão minor com novos recursos de configuração, scraping e PromQL</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -4314,6 +6008,16 @@
           <t>https://github.com/vllm-project/vllm/compare/v0.15.0...v0.15.1</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>patch com correções de segurança, de GPUs Blackwell e bugs diversos</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -4347,6 +6051,16 @@
           <t>https://github.com/vllm-project/vllm/compare/v0.19.0...v0.19.1</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>patch focado em bugs do Gemma 4, junto com a atualização do Transformers</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -4380,6 +6094,16 @@
           <t>https://github.com/vllm-project/vllm/compare/v0.20.0...v0.20.1</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>patch para estabilizar o DeepSeek V4 e corrigir bugs, com ganhos de desempenho</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -4413,6 +6137,16 @@
           <t>https://github.com/vllm-project/vllm/compare/v0.24.0...v0.25.0</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>versão grande com centenas de commits e muitas novidades</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -4446,6 +6180,16 @@
           <t>https://github.com/vllm-project/vllm/compare/v0.27.1...v0.28.0</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>versão grande com foco em desempenho e suporte a novos modelos</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -4479,6 +6223,16 @@
           <t>https://github.com/payloadcms/payload/compare/v3.68.0...v3.68.1</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>única mudança tira da mensagem de erro a sugestão de Next.js vulnerável</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -4512,6 +6266,16 @@
           <t>https://github.com/payloadcms/payload/compare/v3.68.4...v3.68.5</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>corrige o casamento de rotas que considerava a URL do servidor</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -4545,6 +6309,16 @@
           <t>https://github.com/payloadcms/payload/compare/v3.78.0...v3.79.0</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>traz recursos novos no editor lexical e traduções, além de correções</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -4578,6 +6352,16 @@
           <t>https://github.com/payloadcms/payload/compare/v3.84.1...v3.85.0</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>plugin de import/export sai do beta com hooks novos, junto de várias correções</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -4611,6 +6395,16 @@
           <t>https://github.com/payloadcms/payload/compare/v3.87.1...v3.88.0</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>correções de bugs e de segurança, incluindo controle de acesso das chaves de API</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -4644,6 +6438,16 @@
           <t>https://github.com/jgm/pandoc/compare/3.8.1...3.8.2</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>anunciada como correção de regressão no template typst; extensão nova é secundária</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -4677,6 +6481,16 @@
           <t>https://github.com/jgm/pandoc/compare/3.8.2.1...3.8.3</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>adiciona novos formatos de entrada e saída, além de corrigir bugs</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -4710,6 +6524,16 @@
           <t>https://github.com/jgm/pandoc/compare/3.9.0.1...3.9.0.2</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>só corrige uma regressão no template typst da 3.9.0.1</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -4743,6 +6567,16 @@
           <t>https://github.com/jgm/pandoc/compare/3.10.2...3.11</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>novas opções como --math-method e --completion, com algumas correções</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -4776,6 +6610,16 @@
           <t>https://github.com/jgm/pandoc/compare/3.11...3.12</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>foco em desempenho, com várias melhorias e correções menores</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -4809,6 +6653,16 @@
           <t>https://github.com/mattpocock/skills/compare/mattpocock-skills@1.0.0...v1.0.0</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>adiciona a skill ask-matt e novas skills compartilhadas de design</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -4842,6 +6696,16 @@
           <t>https://github.com/mattpocock/skills/compare/v1.0.0...v1.0.1</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>melhora a skill teach para reaproveitar componentes</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -4875,6 +6739,16 @@
           <t>https://github.com/mattpocock/skills/compare/v1.0.1...v1.1.0</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>atualiza o roteador ask-matt e promove a skill code-review</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -4908,6 +6782,16 @@
           <t>https://github.com/mattpocock/skills/compare/v1.2.0...v1.2.2</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>corrige regressão que impedia a skill writing-for-agents de ser acionada automaticamente</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -4941,6 +6825,16 @@
           <t>https://github.com/mattpocock/skills/compare/v1.2.2...v1.2.3</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>correções para não expor segredos e para as skills funcionarem em outros ambientes</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -4974,6 +6868,16 @@
           <t>https://github.com/chakra-ui/chakra-ui/compare/@chakra-ui/react@3.27.0...@chakra-ui/panda-preset@3.27.1</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Patch sem mudanças próprias no panda-preset; o lote mistura ajustes e pequenas novidades.</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -5007,6 +6911,16 @@
           <t>https://github.com/chakra-ui/chakra-ui/compare/@chakra-ui/charts@3.28.0...@chakra-ui/cli@3.28.0</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Minor do lote que traz o componente TagsInput; não tem foco corretivo.</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -5040,6 +6954,16 @@
           <t>https://github.com/chakra-ui/chakra-ui/compare/@chakra-ui/charts@3.29.0...@chakra-ui/react@3.30.0</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Minor com o novo componente Splitter e autoSize no Carousel, além de correções.</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -5073,6 +6997,16 @@
           <t>https://github.com/chakra-ui/chakra-ui/compare/@chakra-ui/panda-preset@3.31.0...@chakra-ui/charts@3.31.0</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Minor do lote com variante nova no ActionBar; as correções são secundárias.</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -5106,6 +7040,16 @@
           <t>https://github.com/chakra-ui/chakra-ui/compare/@chakra-ui/codemod@3.34.0...@chakra-ui/react@3.34.0</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Minor que adiciona o componente DatePicker; correções de exportação vêm junto.</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -5139,6 +7083,16 @@
           <t>https://github.com/fastlane/fastlane/compare/2.228.0...2.229.0</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Minor focada em suporte ao Ruby 3.4 e ajustes de CI.</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -5172,6 +7126,16 @@
           <t>https://github.com/fastlane/fastlane/compare/2.229.0...2.229.1</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Corrige falha no Ruby 3.4 surgida na 2.229.0 e o processo de publicação.</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -5205,6 +7169,16 @@
           <t>https://github.com/fastlane/fastlane/compare/2.231.1...2.232.0</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Minor com novas opções em ações e no match; inclui revert de funcionalidade.</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -5238,6 +7212,16 @@
           <t>https://github.com/fastlane/fastlane/compare/2.232.2...2.233.0</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Minor com várias funcionalidades novas, como upload de vídeo e credenciais STS.</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -5271,6 +7255,16 @@
           <t>https://github.com/fastlane/fastlane/compare/2.234.0...2.235.0</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Minor mista: novidades como thread_ts no Slack e App Clips, além de correções.</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -5304,6 +7298,16 @@
           <t>https://github.com/shadcn-ui/ui/compare/shadcn@3.5.0...shadcn@3.5.1</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Patch da CLI com correções no transform de imports e na instalação de temas.</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -5337,6 +7341,16 @@
           <t>https://github.com/shadcn-ui/ui/compare/shadcn@3.6.2...shadcn@3.6.3</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Patch que mistura validação do nome no create com suporte novo ao OpenCode.</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -5370,6 +7384,16 @@
           <t>https://github.com/shadcn-ui/ui/compare/shadcn@3.8.4...shadcn@3.8.5</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Patch da CLI que só corrige o tratamento de asChild aninhado.</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -5403,6 +7427,16 @@
           <t>https://github.com/shadcn-ui/ui/compare/shadcn@4.7.0...shadcn@4.8.0</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Minor que adiciona o comando registry validate e o campo include.</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -5436,6 +7470,16 @@
           <t>https://github.com/shadcn-ui/ui/compare/shadcn@4.12.0...@shadcn/react@0.2.0</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Primeira versão do pacote @shadcn/react, sem caráter corretivo.</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -5469,6 +7513,16 @@
           <t>https://github.com/sickn33/agentic-awesome-skills/compare/v2.4.0...v2.5.0</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Só adiciona uma skill nova ao catálogo.</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -5502,6 +7556,16 @@
           <t>https://github.com/sickn33/agentic-awesome-skills/compare/v8.3.0...v8.4.0</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Release de descoberta e curadoria de metadados; correções do web-app são secundárias.</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -5535,6 +7599,16 @@
           <t>https://github.com/sickn33/agentic-awesome-skills/compare/v10.9.0...v10.10.0</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Adiciona skills novas, como production-audit, e sincroniza créditos.</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -5568,6 +7642,16 @@
           <t>https://github.com/sickn33/agentic-awesome-skills/compare/v13.0.0...v13.1.0</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Traz três skills novas da comunidade e sincroniza o registro.</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -5601,6 +7685,16 @@
           <t>https://github.com/sickn33/agentic-awesome-skills/compare/v18.9.0...v18.10.0</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Adiciona 124 skills novas e reforça os processos de manutenção.</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -5634,6 +7728,16 @@
           <t>https://github.com/ethereum/go-ethereum/compare/v1.16.4...v1.16.5</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Manutenção para converter provas de blob após o Fusaka, com recursos novos no RPC.</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -5667,6 +7771,16 @@
           <t>https://github.com/ethereum/go-ethereum/compare/v1.16.9...v1.17.0</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Release de funcionalidades do ciclo; as correções de segurança também saíram na v1.16.9.</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -5700,6 +7814,16 @@
           <t>https://github.com/ethereum/go-ethereum/compare/v1.17.2...v1.17.3</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Manutenção com avanço do fork Amsterdam e introdução do ETH/70.</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -5733,6 +7857,16 @@
           <t>https://github.com/ethereum/go-ethereum/compare/v1.17.3...v1.17.4</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Manutenção mista: trabalho do Amsterdam, remoção do Clef e correções acumuladas.</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -5766,6 +7900,16 @@
           <t>https://github.com/ethereum/go-ethereum/compare/v1.17.5...v1.17.6</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Foco em desempenho e no agendamento do Amsterdam na Sepolia.</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -5799,6 +7943,16 @@
           <t>https://github.com/Significant-Gravitas/AutoGPT/compare/autogpt-platform-beta-v0.6.54...autogpt-platform-beta-v0.6.55</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Muitas funcionalidades novas no CoPilot e no painel de custos.</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -5832,6 +7986,16 @@
           <t>https://github.com/Significant-Gravitas/AutoGPT/compare/autogpt-platform-beta-v0.6.56...autogpt-platform-beta-v0.6.57</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Traz várias funcionalidades, como cobrança por assinatura e painel de briefing.</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -5865,6 +8029,16 @@
           <t>https://github.com/Significant-Gravitas/AutoGPT/compare/autogpt-platform-beta-v0.6.57...autogpt-platform-beta-v0.6.58</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Predominam funcionalidades novas: settings v2, tier MAX e notificações push.</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -5898,6 +8072,16 @@
           <t>https://github.com/Significant-Gravitas/AutoGPT/compare/autogpt-platform-beta-v0.6.70...autogpt-platform-beta-v0.7.0</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Funcionalidades novas como Better Auth e marketplace de experts, com algumas correções.</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -5931,6 +8115,16 @@
           <t>https://github.com/Significant-Gravitas/AutoGPT/compare/autogpt-platform-beta-v0.7.2...autogpt-platform-beta-v0.7.3</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Novo sistema de e-mail e melhorias no CoPilot; correções são a parte menor.</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -5964,6 +8158,16 @@
           <t>https://github.com/upstash/context7/compare/v1.0.24...v1.0.25</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Só atualiza a versão do schema no server.json do registro MCP.</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -5997,6 +8201,16 @@
           <t>https://github.com/upstash/context7/compare/ctx7@0.3.8...@upstash/context7-mcp@2.1.6</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Atualiza aviso de filtro e metadados do servidor, sem correção de defeito.</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -6030,6 +8244,16 @@
           <t>https://github.com/upstash/context7/compare/ctx7@0.3.9...@upstash/context7-mcp@2.1.7</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Adiciona a flag --version e melhora o prompt do resolve-library-id.</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -6063,6 +8287,16 @@
           <t>https://github.com/upstash/context7/compare/ctx7@0.3.12...@upstash/context7-mcp@2.1.8</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Corrige a perda das CAs padrão do Node ao usar NODE_EXTRA_CA_CERTS.</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -6096,6 +8330,16 @@
           <t>https://github.com/upstash/context7/compare/ctx7@0.4.5...ctx7@0.5.0</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Adiciona login OAuth por device code na CLI.</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -6129,6 +8373,16 @@
           <t>https://github.com/xtekky/gpt4free/compare/v6.5.5...v6.5.6</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Adiciona MarkItDownTool, TextToAudioTool e CORS no servidor MCP; só um ajuste é corretivo.</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -6162,6 +8416,16 @@
           <t>https://github.com/xtekky/gpt4free/compare/v7.1.4...v7.1.5</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Corrige a assinatura de get_quota, que quebrava a rota de quota criada na v7.1.4.</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -6195,6 +8459,16 @@
           <t>https://github.com/xtekky/gpt4free/compare/v7.4.6...v7.4.7</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Só troca argumentos posicionais por nomeados em create_func, por legibilidade.</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -6228,6 +8502,16 @@
           <t>https://github.com/xtekky/gpt4free/compare/v7.9.2...v7.9.3</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Apenas remove dependências dos requirements e do setup.py, sem defeito apontado.</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -6261,6 +8545,16 @@
           <t>https://github.com/xtekky/gpt4free/compare/v8.1.8...v8.2.0</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Launcher g4f-go passa a rodar scripts Python; inclui um pequeno ajuste de caminho.</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -6294,6 +8588,16 @@
           <t>https://github.com/langgenius/dify/compare/1.9.1...1.9.2</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Muitas refatorações e melhorias de estabilidade, com troca do cliente do Weaviate.</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -6327,6 +8631,16 @@
           <t>https://github.com/langgenius/dify/compare/1.11.3...1.11.4</t>
         </is>
       </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Hotfix: atualiza o Node por causa de CVE e corrige três bugs.</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -6360,6 +8674,16 @@
           <t>https://github.com/langgenius/dify/compare/1.11.4...1.12.0</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Minor que lança o Summary Index na base de conhecimento.</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -6393,6 +8717,16 @@
           <t>https://github.com/langgenius/dify/compare/1.13.3...1.14.0</t>
         </is>
       </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Minor com colaboração em tempo real e API de human-in-the-loop.</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -6426,6 +8760,16 @@
           <t>https://github.com/langgenius/dify/compare/1.14.1...1.14.2</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Patch focado em correções de segurança e confiabilidade, com poucas novidades.</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -6459,6 +8803,16 @@
           <t>https://github.com/roboflow/supervision/compare/0.26.1...0.27.0</t>
         </is>
       </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Minor com várias funções novas, como filter_segments_by_distance e edit_distance.</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -6492,6 +8846,16 @@
           <t>https://github.com/roboflow/supervision/compare/0.29.0.post0...0.29.1</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>O destaque é o novo KeyPoints.with_nms; correções e otimizações vêm junto.</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -6525,6 +8889,16 @@
           <t>https://github.com/roboflow/supervision/compare/0.30.1...0.30.2</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Release só de correções numéricas em utilitários de detecção, sem API nova.</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -6558,6 +8932,16 @@
           <t>https://github.com/roboflow/supervision/compare/0.30.2...0.30.3</t>
         </is>
       </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Release de correções de travamentos e resultados errados em pose, VLM e vídeo.</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -6591,6 +8975,16 @@
           <t>https://github.com/roboflow/supervision/compare/0.30.4...0.30.5</t>
         </is>
       </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Patch que corrige 11 bugs de cálculo e travamento, sem API nova.</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -6624,6 +9018,16 @@
           <t>https://github.com/Fission-AI/OpenSpec/compare/v1.0.2...v1.1.0</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>release de estabilidade focada em corrigir problemas de caminho e de arquivamento</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -6657,6 +9061,16 @@
           <t>https://github.com/Fission-AI/OpenSpec/compare/v1.1.0...v1.1.1</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>patch rápido só para corrigir o formato das referências de comandos gerados</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -6690,6 +9104,16 @@
           <t>https://github.com/Fission-AI/OpenSpec/compare/v1.7.0...v1.8.0</t>
         </is>
       </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>traz novos alvos de integração e recursos no archive, além de correções</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -6723,6 +9147,16 @@
           <t>https://github.com/Fission-AI/OpenSpec/compare/v1.9.0...v1.10.0</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>adiciona suporte a novo editor e opção de idioma, com correções menores</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -6756,6 +9190,16 @@
           <t>https://github.com/Fission-AI/OpenSpec/compare/v1.10.0...v1.11.0</t>
         </is>
       </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>novos comandos show --diff e status --all; correções ficam em segundo plano</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -6789,6 +9233,16 @@
           <t>https://github.com/mastodon/mastodon/compare/v4.4.7...v4.4.8</t>
         </is>
       </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>release só de segurança, corrige bypass no controle de citações</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -6822,6 +9276,16 @@
           <t>https://github.com/mastodon/mastodon/compare/v4.4.9...v4.5.2</t>
         </is>
       </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>patch da 4.5 com quase só correções de bugs recentes</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -6855,6 +9319,16 @@
           <t>https://github.com/mastodon/mastodon/compare/v4.4.11...v4.3.17</t>
         </is>
       </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>patch da 4.3 com duas correções de segurança e uma de bug</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -6888,6 +9362,16 @@
           <t>https://github.com/mastodon/mastodon/compare/v4.5.8...v4.4.15</t>
         </is>
       </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>patch da 4.4 motivado por falhas de segurança, com várias correções de bugs</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -6921,6 +9405,16 @@
           <t>https://github.com/mastodon/mastodon/compare/v4.6.3...v4.6.4</t>
         </is>
       </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>patch com correções de segurança e uma longa lista de bugs corrigidos</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -6954,6 +9448,16 @@
           <t>https://github.com/Mintplex-Labs/anything-llm/compare/v1.8.5...v1.9.0</t>
         </is>
       </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>grande reformulação do modo @agent, com streaming e novas integrações</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -6987,6 +9491,16 @@
           <t>https://github.com/Mintplex-Labs/anything-llm/compare/v1.9.0...v1.9.1</t>
         </is>
       </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>traz suporte a PWA, novos conectores e provedores; correções são minoria</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -7020,6 +9534,16 @@
           <t>https://github.com/Mintplex-Labs/anything-llm/compare/v1.11.1...v1.11.2</t>
         </is>
       </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>melhorias de interface e novo modo de chat, além de algumas correções</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -7053,6 +9577,16 @@
           <t>https://github.com/Mintplex-Labs/anything-llm/compare/v1.14.1...v1.14.2</t>
         </is>
       </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>chamada de patches, mas inclui novos provedores de busca e de voz</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -7086,6 +9620,16 @@
           <t>https://github.com/Mintplex-Labs/anything-llm/compare/v1.16.1...v1.16.2</t>
         </is>
       </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>várias funcionalidades novas, como novos provedores e geração de imagens</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -7119,6 +9663,16 @@
           <t>https://github.com/Imbad0202/academic-research-skills/compare/v3.9.4.2...v3.10.0</t>
         </is>
       </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>versão minor com nova camada de políticas, avaliação e guarda de escrita</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -7152,6 +9706,16 @@
           <t>https://github.com/Imbad0202/academic-research-skills/compare/v3.10.0...v3.11.0</t>
         </is>
       </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>adiciona verificação determinística de existência das citações</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -7185,6 +9749,16 @@
           <t>https://github.com/Imbad0202/academic-research-skills/compare/v3.17.0...v3.18.0</t>
         </is>
       </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>conjunto de recursos novos, como lembrete de atualização e avisos de escopo</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -7218,6 +9792,16 @@
           <t>https://github.com/Imbad0202/academic-research-skills/compare/v3.19.0...v3.20.0</t>
         </is>
       </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>agrupa cem commits com novos contratos de revisão e recursos de integridade</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -7251,6 +9835,16 @@
           <t>https://github.com/Imbad0202/academic-research-skills/compare/v3.20.0...v3.20.1</t>
         </is>
       </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>apesar de ser patch, traz principalmente recursos novos de avaliação</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -7284,6 +9878,16 @@
           <t>https://github.com/pingcap/tidb/compare/v7.5.7...v8.5.4</t>
         </is>
       </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>patch da 8.5 com funcionalidades novas além das correções de bugs</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -7317,6 +9921,16 @@
           <t>https://github.com/pingcap/tidb/compare/v8.5.4...v8.5.5</t>
         </is>
       </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>traz recursos novos, como pushdown de index lookup, junto com correções</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -7350,6 +9964,16 @@
           <t>https://github.com/pingcap/tidb/compare/v8.5.5...v8.5.6</t>
         </is>
       </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>inclui privilégios por coluna e regras de slow log, não só correções</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -7383,6 +10007,16 @@
           <t>https://github.com/pingcap/tidb/compare/v8.5.7...v8.5.8</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>sem funcionalidades novas; a maioria das mudanças corrige bugs e falhas de segurança</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -7416,6 +10050,16 @@
           <t>https://github.com/pingcap/tidb/compare/v8.5.8...v7.5.8</t>
         </is>
       </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>patch da 7.5 com correções de travamentos e falhas, quase nada além disso</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -7449,6 +10093,16 @@
           <t>https://github.com/ggml-org/llama.cpp/compare/b8600...b8601</t>
         </is>
       </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>único commit corrige falha de parsing que deixava a resposta vazia</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -7482,6 +10136,16 @@
           <t>https://github.com/ggml-org/llama.cpp/compare/b9748...b9750</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>adiciona callback de progresso e implementa a instrução call nos templates</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -7515,6 +10179,16 @@
           <t>https://github.com/ggml-org/llama.cpp/compare/b9789...b9802</t>
         </is>
       </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>mistura recursos novos, como subcomando de download, com algumas correções</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -7548,6 +10222,16 @@
           <t>https://github.com/ggml-org/llama.cpp/compare/b9935...b9936</t>
         </is>
       </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>corrige regressão de desempenho no servidor ao dividir lotes de entrada</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -7581,6 +10265,16 @@
           <t>https://github.com/ggml-org/llama.cpp/compare/b10258...b10259</t>
         </is>
       </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>mudança no carregamento feita para corrigir saída corrompida e abortos em CPU</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -7614,6 +10308,16 @@
           <t>https://github.com/ChrisTitusTech/winutil/compare/25.09.05...25.10.06</t>
         </is>
       </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>novo botão de restauração e modo offline junto com várias correções</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -7647,6 +10351,16 @@
           <t>https://github.com/ChrisTitusTech/winutil/compare/26.02.11...26.02.18</t>
         </is>
       </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>novos recursos como exportar configurações e destacar apps livres, além de correções</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -7680,6 +10394,16 @@
           <t>https://github.com/ChrisTitusTech/winutil/compare/26.02.18...26.03.03</t>
         </is>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>principal novidade é o criador de ISO do Windows 11</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -7713,6 +10437,16 @@
           <t>https://github.com/ChrisTitusTech/winutil/compare/26.04.21...26.04.30</t>
         </is>
       </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>novos ajustes adicionados junto com poucas correções de instalação</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -7746,6 +10480,16 @@
           <t>https://github.com/ChrisTitusTech/winutil/compare/26.05.12...26.06.23</t>
         </is>
       </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>agrupa mais de cem commits com recursos, limpezas e correções</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -7779,6 +10523,16 @@
           <t>https://github.com/crewAIInc/crewAI/compare/0.201.1...0.203.0</t>
         </is>
       </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>mistura melhorias no Agent, documentação e poucas correções</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -7812,6 +10566,16 @@
           <t>https://github.com/crewAIInc/crewAI/compare/1.2.0...1.2.1</t>
         </is>
       </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>adiciona integração de observabilidade e suporte a apps no liteagent</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -7845,6 +10609,16 @@
           <t>https://github.com/crewAIInc/crewAI/compare/1.15.11...1.15.12</t>
         </is>
       </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>traz recursos novos, como leitura de URLs e comando create unificado</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -7878,6 +10652,16 @@
           <t>https://github.com/crewAIInc/crewAI/compare/1.15.17...1.15.18</t>
         </is>
       </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>muitas correções, mas também vários recursos novos em flows conversacionais</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -7911,6 +10695,16 @@
           <t>https://github.com/crewAIInc/crewAI/compare/1.15.18...1.15.19</t>
         </is>
       </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>recursos novos misturados com correções e atualizações de segurança de dependências</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -7944,6 +10738,16 @@
           <t>https://github.com/ToolJet/ToolJet/compare/v3.20.28-lts...v3.20.29-lts</t>
         </is>
       </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>traz fluxo OIDC PKCE e métricas novas; só uma correção de SSO</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -7977,6 +10781,16 @@
           <t>https://github.com/ToolJet/ToolJet/compare/v3.20.168-lts...v3.20.169-lts</t>
         </is>
       </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>duas correções pequenas: autocompletar de consultas e overflow em container e form</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -8010,6 +10824,16 @@
           <t>https://github.com/ToolJet/ToolJet/compare/v3.20.172-lts...v3.20.173-lts</t>
         </is>
       </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>adiciona suporte RunJS Agent e evento de refresh na tabela</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -8043,6 +10867,16 @@
           <t>https://github.com/ToolJet/ToolJet/compare/v3.20.187-lts...v3.20.188-lts</t>
         </is>
       </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>três correções de bugs em botão, evento de navegação e consultas</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -8076,6 +10910,16 @@
           <t>https://github.com/ToolJet/ToolJet/compare/v3.20.230-lts...v3.20.231-lts</t>
         </is>
       </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>traz biblioteca de componentes customizados e melhorias no widget de navegação</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -8109,6 +10953,16 @@
           <t>https://github.com/browser-use/browser-use/compare/0.10.0...0.10.1</t>
         </is>
       </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>refeita no mesmo dia só para corrigir a versão esquecida no pyproject</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -8142,6 +10996,16 @@
           <t>https://github.com/browser-use/browser-use/compare/0.11.2...0.11.3</t>
         </is>
       </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>várias novidades, como gravação multiaba e skills externas, junto de correções</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -8175,6 +11039,16 @@
           <t>https://github.com/browser-use/browser-use/compare/0.12.0...0.12.1</t>
         </is>
       </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>patch quase todo de correções de bugs, sem funcionalidade nova</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -8208,6 +11082,16 @@
           <t>https://github.com/browser-use/browser-use/compare/0.12.9...0.13.0</t>
         </is>
       </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>introduz novo agente beta escrito em Rust</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -8241,6 +11125,16 @@
           <t>https://github.com/browser-use/browser-use/compare/0.13.5...0.13.6</t>
         </is>
       </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>apenas sobe a versão e sincroniza componente com novo fluxo de gravação</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -8274,6 +11168,16 @@
           <t>https://github.com/danielmiessler/Fabric/compare/v1.4.338...v1.4.339</t>
         </is>
       </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>adiciona suporte a anexar imagens para modelos de visao no Ollama</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -8307,6 +11211,16 @@
           <t>https://github.com/danielmiessler/Fabric/compare/v1.4.362...v1.4.363</t>
         </is>
       </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>refatoracao para reaproveitar o cliente HTTP e simplificar mensagens de erro</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -8340,6 +11254,16 @@
           <t>https://github.com/danielmiessler/Fabric/compare/v1.4.431...v1.4.432</t>
         </is>
       </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>atualizacao de dependencias do frontend web, sem defeito de usuario descrito</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -8373,6 +11297,16 @@
           <t>https://github.com/danielmiessler/Fabric/compare/v1.4.468...v1.4.469</t>
         </is>
       </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>troca o processamento de PDF por um worker WASM; correcoes sao secundarias</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -8406,6 +11340,16 @@
           <t>https://github.com/danielmiessler/Fabric/compare/v1.4.476...v1.4.477</t>
         </is>
       </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>corrige vazamento de diretorios temporarios no carregador de padroes</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -8439,6 +11383,16 @@
           <t>https://github.com/career-ops-hq/career-ops/compare/career-ops-v1.14.0...career-ops-v1.15.0</t>
         </is>
       </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>sistema de plugins, novos provedores de vagas e atalhos no painel</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -8472,6 +11426,16 @@
           <t>https://github.com/career-ops-hq/career-ops/compare/web-v0.2.0...career-ops-v1.18.0</t>
         </is>
       </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>varias funcionalidades novas, como classificacao de respostas e novos idiomas</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -8505,6 +11469,16 @@
           <t>https://github.com/career-ops-hq/career-ops/compare/career-ops-v1.33.0...web-v0.11.0</t>
         </is>
       </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>onze correcoes de bugs no painel web e uma unica opcao nova</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -8538,6 +11512,16 @@
           <t>https://github.com/career-ops-hq/career-ops/compare/web-v0.11.0...career-ops-v1.34.0</t>
         </is>
       </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>atualizador passa a seguir releases, alem de novas fontes e melhorias na busca</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -8571,6 +11555,16 @@
           <t>https://github.com/career-ops-hq/career-ops/compare/web-v0.12.0...career-ops-v1.35.0</t>
         </is>
       </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>nove novas fontes de vagas e perfil de carreira revisado item a item</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -8604,6 +11598,16 @@
           <t>https://github.com/vercel-labs/agent-browser/compare/v0.7.4...v0.7.5</t>
         </is>
       </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>corrige o workflow que falhava ao publicar binarios em release ja existente</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -8637,6 +11641,16 @@
           <t>https://github.com/vercel-labs/agent-browser/compare/v0.8.3...v0.8.4</t>
         </is>
       </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>corrige o erro Daemon not found ao resolver links simbolicos do executavel</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -8670,6 +11684,16 @@
           <t>https://github.com/vercel-labs/agent-browser/compare/agent-browser@0.23.0...v0.23.0</t>
         </is>
       </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>lanca o dashboard; as correcoes para Windows acompanham a novidade</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -8703,6 +11727,16 @@
           <t>https://github.com/vercel-labs/agent-browser/compare/v0.25.4...v0.25.5</t>
         </is>
       </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>patch so com correcoes: auto-connect, viewport da gravacao, get box e abas</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -8736,6 +11770,16 @@
           <t>https://github.com/vercel-labs/agent-browser/compare/v0.27.3...v0.28.0</t>
         </is>
       </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>adiciona servidor MCP e sistema de plugins</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -8769,6 +11813,16 @@
           <t>https://github.com/ant-design/ant-design/compare/6.3.4...6.3.5</t>
         </is>
       </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>patch com tres correcoes: Image, TimePicker em touch e centralizacao de Icon</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -8802,6 +11856,16 @@
           <t>https://github.com/ant-design/ant-design/compare/6.3.5...6.3.6</t>
         </is>
       </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>patch quase todo de correcoes em componentes, com dois ajustes de desempenho</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -8835,6 +11899,16 @@
           <t>https://github.com/ant-design/ant-design/compare/6.5.0...6.5.1</t>
         </is>
       </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>patch so com correcoes em componentes, incluindo comportamentos restaurados</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -8868,6 +11942,16 @@
           <t>https://github.com/ant-design/ant-design/compare/6.5.2...6.5.3</t>
         </is>
       </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>patch com correcoes em Input.OTP, DatePicker, Form, Slider e outros</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -8901,6 +11985,16 @@
           <t>https://github.com/ant-design/ant-design/compare/6.5.3...6.5.4</t>
         </is>
       </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>patch so com correcoes em Alert, Checkbox, Table, Transfer e outros</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -8934,6 +12028,16 @@
           <t>https://github.com/ccxt/ccxt/compare/v4.5.7...v4.5.8</t>
         </is>
       </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>mistura recursos novos e correcoes em varias exchanges</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -8967,6 +12071,16 @@
           <t>https://github.com/ccxt/ccxt/compare/v4.5.25...v4.5.26</t>
         </is>
       </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>unica mudanca corrige o tratamento de erros da bitmart</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -9000,6 +12114,16 @@
           <t>https://github.com/ccxt/ccxt/compare/v4.5.29...v4.5.30</t>
         </is>
       </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>inclui integracao de exchange nova e metodos novos, alem de correcoes</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -9033,6 +12157,16 @@
           <t>https://github.com/ccxt/ccxt/compare/v4.5.37...v4.5.38</t>
         </is>
       </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>onze das catorze mudancas sao correcoes em exchanges</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -9066,6 +12200,16 @@
           <t>https://github.com/ccxt/ccxt/compare/v4.5.38...v4.5.39</t>
         </is>
       </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>varios metodos e endpoints novos, com algumas correcoes no meio</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -9099,6 +12243,16 @@
           <t>https://github.com/apple/container/compare/0.4.1...0.5.0</t>
         </is>
       </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>novos comandos e mudancas incompativeis na CLI e na API</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -9132,6 +12286,16 @@
           <t>https://github.com/apple/container/compare/0.5.0...0.6.0</t>
         </is>
       </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>adiciona volumes anonimos, --subnet e rede none, entre outras novidades</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -9165,6 +12329,16 @@
           <t>https://github.com/apple/container/compare/0.11.0...0.12.0</t>
         </is>
       </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>novos modos de saida, suporte a capabilities e configuracao em TOML</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -9198,6 +12372,16 @@
           <t>https://github.com/apple/container/compare/1.2.1...1.2.2</t>
         </is>
       </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>corrige falha que impedia o container k8s no pacote de instalacao</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -9231,6 +12415,16 @@
           <t>https://github.com/apple/container/compare/1.3.0...1.3.1</t>
         </is>
       </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>patch de seguranca para vulnerabilidades no pacote Containerization</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -9264,6 +12458,16 @@
           <t>https://github.com/reactive-resume/reactive-resume/compare/v5.1.2...v5.1.3</t>
         </is>
       </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>novo template e melhorias no builder; correcoes de PDF vem junto</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -9297,6 +12501,16 @@
           <t>https://github.com/reactive-resume/reactive-resume/compare/v5.1.3...v5.1.4</t>
         </is>
       </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>lanca o workspace de agente para editar curriculos, entre outras novidades</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -9330,6 +12544,16 @@
           <t>https://github.com/reactive-resume/reactive-resume/compare/v5.2.2...v5.2.3</t>
         </is>
       </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>mais provedores de modelos nas configuracoes e exportacao de carta mais limpa</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -9363,6 +12587,16 @@
           <t>https://github.com/reactive-resume/reactive-resume/compare/v5.2.4...v5.2.5</t>
         </is>
       </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>traz CSS semantico e trabalho de SEO junto com algumas correcoes</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -9396,6 +12630,16 @@
           <t>https://github.com/reactive-resume/reactive-resume/compare/v5.2.5...v5.2.6</t>
         </is>
       </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>verificacao de ATS, carta via MCP e CSS semantico como padrao</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -9429,6 +12673,16 @@
           <t>https://github.com/rails/rails/compare/v8.0.3...v8.1.0</t>
         </is>
       </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>versao minor com recursos novos e remocao de APIs obsoletas</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -9462,6 +12716,16 @@
           <t>https://github.com/rails/rails/compare/v8.1.0...v7.0.9</t>
         </is>
       </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>manutencao do ramo 7.0 so com correcoes e ajustes para Ruby 3.4</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -9495,6 +12759,16 @@
           <t>https://github.com/rails/rails/compare/v7.0.10...v7.1.6</t>
         </is>
       </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>patch com correcoes de conexao e concorrencia no Active Record</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -9528,6 +12802,16 @@
           <t>https://github.com/rails/rails/compare/v7.2.3...v8.0.4</t>
         </is>
       </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>patch do ramo 8.0 com correcoes, entre elas perda de dados no SQLite</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -9561,6 +12845,16 @@
           <t>https://github.com/rails/rails/compare/v8.1.2...v7.2.3.1</t>
         </is>
       </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>release de seguranca que corrige varias CVEs</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -9594,6 +12888,16 @@
           <t>https://github.com/fastapi/fastapi/compare/0.118.0...0.118.1</t>
         </is>
       </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>ajuste de compatibilidade com Pydantic 2.12, alem de docs e traducoes</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -9627,6 +12931,16 @@
           <t>https://github.com/fastapi/fastapi/compare/0.123.5...0.123.6</t>
         </is>
       </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>corrige o suporte a functools wraps e partial combinados</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -9660,6 +12974,16 @@
           <t>https://github.com/fastapi/fastapi/compare/0.128.3...0.128.4</t>
         </is>
       </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>refatoracao interna e traducoes, sem correcao de defeito</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -9693,6 +13017,16 @@
           <t>https://github.com/fastapi/fastapi/compare/0.134.0...0.135.0</t>
         </is>
       </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>adiciona suporte a Server Sent Events</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -9726,6 +13060,16 @@
           <t>https://github.com/fastapi/fastapi/compare/0.139.1...0.139.2</t>
         </is>
       </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>corrige montagem de rotas que nao era thread-safe</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -9759,6 +13103,16 @@
           <t>https://github.com/react-hook-form/react-hook-form/compare/v7.70.0...v7.71.0</t>
         </is>
       </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>foco em desempenho do contexto, com uma unica correcao</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -9792,6 +13146,16 @@
           <t>https://github.com/react-hook-form/react-hook-form/compare/v7.74.0...v7.75.0</t>
         </is>
       </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>muda dirtyFields e adota TypeScript 6; as correcoes nao sao o foco</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -9825,6 +13189,16 @@
           <t>https://github.com/react-hook-form/react-hook-form/compare/v7.76.0...v7.76.1</t>
         </is>
       </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>patch com correcoes em setValues e reversao de uma correcao problematica</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -9858,6 +13232,16 @@
           <t>https://github.com/react-hook-form/react-hook-form/compare/v7.81.0...v7.82.0</t>
         </is>
       </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>nova opcao delayError e ganho de desempenho, alem de correcoes</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -9891,6 +13275,16 @@
           <t>https://github.com/react-hook-form/react-hook-form/compare/v7.85.0...v7.86.0</t>
         </is>
       </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>nova API getErrors e melhorias de desempenho junto com varias correcoes</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -9924,6 +13318,16 @@
           <t>https://github.com/moeru-ai/airi/compare/v0.8.1-beta.4...v0.8.1-beta.11</t>
         </is>
       </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>Traz captura de tela, reconhecimento de voz e outras novidades além de correções</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -9957,6 +13361,16 @@
           <t>https://github.com/moeru-ai/airi/compare/v0.8.1...v0.8.2</t>
         </is>
       </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>Mistura correções com recursos novos, como sessões locais e novo provedor</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -9990,6 +13404,16 @@
           <t>https://github.com/moeru-ai/airi/compare/v0.9.0-alpha.24...v0.9.0-alpha.28</t>
         </is>
       </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>Notas só com correções: estado do chat, módulo de audição e links da documentação</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -10023,6 +13447,16 @@
           <t>https://github.com/moeru-ai/airi/compare/v0.9.0-beta.2...v0.9.0</t>
         </is>
       </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>Versão estável com muitas novidades, como integração com Minecraft e login OIDC</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -10056,6 +13490,16 @@
           <t>https://github.com/moeru-ai/airi/compare/v0.11.3...v0.12.0-beta.5</t>
         </is>
       </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>Destaca novidades no Live2D e provedores de voz, com correções em segundo plano</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -10089,6 +13533,16 @@
           <t>https://github.com/janhq/jan/compare/v0.6.10...v0.7.0</t>
         </is>
       </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>Muitas funcionalidades novas, como seletor de modelos e MCP na versão web</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -10122,6 +13576,16 @@
           <t>https://github.com/janhq/jan/compare/v0.7.4...v0.7.5</t>
         </is>
       </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>Apenas correções: importação de modelos no Windows, backend CUDA e processo MCP</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -10155,6 +13619,16 @@
           <t>https://github.com/janhq/jan/compare/v0.7.8...v0.7.9</t>
         </is>
       </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>Mistura grande de docs e correções com várias funcionalidades novas</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -10188,6 +13662,16 @@
           <t>https://github.com/janhq/jan/compare/v0.8.0...v0.8.1</t>
         </is>
       </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>Primeiro patch após a 0.8.0, dominado por correções e itens de configurações restaurados</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -10221,6 +13705,16 @@
           <t>https://github.com/janhq/jan/compare/v0.8.2...v0.8.3</t>
         </is>
       </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>Traz entrada de vídeo, artefatos HTML e ramificação de mensagens, entre outras novidades</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -10254,6 +13748,16 @@
           <t>https://github.com/rtk-ai/rtk/compare/v0.2.0...v0.2.1</t>
         </is>
       </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>Adiciona suporte a pnpm e ao Vitest</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -10287,6 +13791,16 @@
           <t>https://github.com/rtk-ai/rtk/compare/v0.8.1...v0.9.0</t>
         </is>
       </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>Várias funcionalidades novas, como rtk tree e passthrough de subcomandos</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -10320,6 +13834,16 @@
           <t>https://github.com/rtk-ai/rtk/compare/v0.13.1...v0.14.0</t>
         </is>
       </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>Ajusta URLs e metadados após mudança de organização e automatiza fórmula do Homebrew</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -10353,6 +13877,16 @@
           <t>https://github.com/rtk-ai/rtk/compare/v0.40.0...v0.41.0</t>
         </is>
       </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>Quase só correções em filtros, git, truncamento e instalação; apenas uma novidade</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -10386,6 +13920,16 @@
           <t>https://github.com/rtk-ai/rtk/compare/v0.44.2...v0.45.0</t>
         </is>
       </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>Novidades principais: hooks para Mistral Vibe e reescrita de blocos multilinha</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -10419,6 +13963,16 @@
           <t>https://github.com/calcom/cal.diy/compare/v5.7.7...v5.7.8</t>
         </is>
       </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>Release periódica misturando funcionalidades, refatorações e correções, sem foco corretivo</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -10452,6 +14006,16 @@
           <t>https://github.com/calcom/cal.diy/compare/v5.7.11...v5.7.12</t>
         </is>
       </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>Várias funcionalidades novas, como gatilhos de workflow e bloqueio de spam</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -10485,6 +14049,16 @@
           <t>https://github.com/calcom/cal.diy/compare/v5.8.14...v5.9.0</t>
         </is>
       </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>Única mudança corrige o fuso horário usado nos insights de roteamento</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -10518,6 +14092,16 @@
           <t>https://github.com/calcom/cal.diy/compare/v6.0.10...v6.0.11</t>
         </is>
       </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>Mistura de funcionalidades, tarefas internas e correções sem foco corretivo</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -10551,6 +14135,16 @@
           <t>https://github.com/calcom/cal.diy/compare/v6.1.1...v6.1.2</t>
         </is>
       </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>Release periódica com várias funcionalidades novas junto das correções</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -10584,6 +14178,16 @@
           <t>https://github.com/zed-industries/zed/compare/v0.212.7...v0.213.3</t>
         </is>
       </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>Release semanal com várias funcionalidades novas, como sticky scroll e novos modelos</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -10617,6 +14221,16 @@
           <t>https://github.com/zed-industries/zed/compare/v0.217.1...v0.217.2</t>
         </is>
       </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>Adiciona o modelo Gemini 3 Flash e suporte às versões beta do ty</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -10650,6 +14264,16 @@
           <t>https://github.com/zed-industries/zed/compare/v0.220.2...v0.220.3</t>
         </is>
       </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>Corrige regressão nas permissões padrão de comandos do terminal no agente</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -10683,6 +14307,16 @@
           <t>https://github.com/zed-industries/zed/compare/v0.224.6...v0.224.7</t>
         </is>
       </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>Patch feito para lançar o Gemini 3.1 Pro; correção de pânico veio junto</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -10716,6 +14350,16 @@
           <t>https://github.com/zed-industries/zed/compare/v1.13.1...v1.13.2</t>
         </is>
       </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>Correções de pânico, atalho Option+Left e cores do Gruvbox, mais um ajuste de docs</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -10749,6 +14393,16 @@
           <t>https://github.com/typst/typst/compare/v0.13.1...v0.14.0</t>
         </is>
       </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>Versão grande com PDF acessível, exportação HTML ampliada e muitos recursos novos</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -10782,6 +14436,16 @@
           <t>https://github.com/typst/typst/compare/v0.14.0...v0.14.1</t>
         </is>
       </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>Corrige regressões e travamentos que vieram com a nova exportação PDF da 0.14.0</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -10815,6 +14479,16 @@
           <t>https://github.com/typst/typst/compare/v0.14.1...v0.14.2</t>
         </is>
       </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>Atualiza o runtime WebAssembly para fechar uma vulnerabilidade de memória</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -10848,6 +14522,16 @@
           <t>https://github.com/typst/typst/compare/v0.14.2...v0.15.0</t>
         </is>
       </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>Versão grande com fontes variáveis, exportação em bundle e várias novidades</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -10881,6 +14565,16 @@
           <t>https://github.com/typst/typst/compare/v0.15.0...v0.15.1</t>
         </is>
       </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>Corrige regressões em matemática e outros bugs de layout e exportação após a 0.15.0</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -10914,6 +14608,16 @@
           <t>https://github.com/denoland/deno/compare/v2.7.7...v2.7.8</t>
         </is>
       </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>Patch semanal de rotina com seis funcionalidades novas e correções de compatibilidade</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -10947,6 +14651,16 @@
           <t>https://github.com/denoland/deno/compare/v2.7.8...v2.7.9</t>
         </is>
       </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>Saiu dois dias depois quase só com correções, incluindo o deno compile</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -10980,6 +14694,16 @@
           <t>https://github.com/denoland/deno/compare/v2.8.2...v2.8.3</t>
         </is>
       </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>Traz dezenas de funcionalidades novas, como watch no compile e recursos de LSP</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -11013,6 +14737,16 @@
           <t>https://github.com/denoland/deno/compare/v2.9.0...v2.9.1</t>
         </is>
       </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>Primeiro patch após a 2.9.0, quase só correções, muitas do deno desktop recém-lançado</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -11046,6 +14780,16 @@
           <t>https://github.com/denoland/deno/compare/v2.9.1...v2.9.2</t>
         </is>
       </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>Dez funcionalidades novas, sobretudo no desktop, junto das correções e otimizações</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -11079,6 +14823,16 @@
           <t>https://github.com/dani-garcia/vaultwarden/compare/1.34.3...1.35.0</t>
         </is>
       </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>Adiciona login SSO com OpenID Connect e atualiza o web vault</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -11112,6 +14866,16 @@
           <t>https://github.com/dani-garcia/vaultwarden/compare/1.35.4...1.35.5</t>
         </is>
       </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>Focada em três falhas de segurança, com várias outras correções junto</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -11145,6 +14909,16 @@
           <t>https://github.com/dani-garcia/vaultwarden/compare/1.35.8...1.36.0</t>
         </is>
       </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>Abre com seis falhas de segurança corrigidas; arquivamento de itens vem como extra</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -11178,6 +14952,16 @@
           <t>https://github.com/dani-garcia/vaultwarden/compare/1.37.0...1.37.1</t>
         </is>
       </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>Corrige convites de organização e imagens Alpine com problema no OpenSSL</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -11211,6 +14995,16 @@
           <t>https://github.com/dani-garcia/vaultwarden/compare/1.37.1...1.37.2</t>
         </is>
       </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>Corrige incompatibilidade que fazia clientes 2026.8 falharem; resto são ajustes pequenos</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -11244,6 +15038,16 @@
           <t>https://github.com/nexu-io/open-design/compare/open-design-v0.4.1...open-design-v0.5.0</t>
         </is>
       </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>Muitas novidades, como dashboards com dados ao vivo e modo Inspect</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -11277,6 +15081,16 @@
           <t>https://github.com/nexu-io/open-design/compare/open-design-v0.12.0...open-design-v0.13.0</t>
         </is>
       </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>Foco em novidades: retomada de sessão, presets de BYOK e carteira da nuvem</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -11310,6 +15124,16 @@
           <t>https://github.com/nexu-io/open-design/compare/open-design-v0.15.0...open-design-v0.15.1</t>
         </is>
       </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>Apresentada como upgrade do agente, com recursos novos além das correções</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -11343,6 +15167,16 @@
           <t>https://github.com/nexu-io/open-design/compare/open-design-v0.20.2...open-design-v0.21.0</t>
         </is>
       </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>Release temática de confiabilidade; correções predominam sobre poucas novidades</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -11376,6 +15210,16 @@
           <t>https://github.com/nexu-io/open-design/compare/open-design-v0.23.0...open-design-v0.24.0</t>
         </is>
       </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>Focada em manter execuções e prévias intactas; correções são a maior parte</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -11409,6 +15253,16 @@
           <t>https://github.com/JuliaLang/julia/compare/v1.11.7...v1.12.0</t>
         </is>
       </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>Nova versão menor da linguagem, com muitas funcionalidades novas</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -11442,6 +15296,16 @@
           <t>https://github.com/JuliaLang/julia/compare/v1.12.3...v1.12.4</t>
         </is>
       </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>Patch da série 1.12 com correções retroportadas, incluindo estouro de buffer</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -11475,6 +15339,16 @@
           <t>https://github.com/JuliaLang/julia/compare/v1.10.11...v1.12.6</t>
         </is>
       </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>Patch da série 1.12 com correções retroportadas; commits listados não são desta versão</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -11508,6 +15382,16 @@
           <t>https://github.com/JuliaLang/julia/compare/v1.12.7...v1.10.12</t>
         </is>
       </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>Patch do LTS 1.10 com correções de build e retroportes, sem novidades</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -11539,6 +15423,16 @@
       <c r="G301" s="2" t="inlineStr">
         <is>
           <t>https://github.com/JuliaLang/julia/compare/v1.10.12...v1.13.0</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>Nova versão menor da linguagem, com funcionalidades novas</t>
         </is>
       </c>
     </row>
